--- a/code/experiment/1024chunk_BGE-M3-10topk_Y.xlsx
+++ b/code/experiment/1024chunk_BGE-M3-10topk_Y.xlsx
@@ -5,17 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D3C062-66C1-4434-86FF-FACE2172478B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3BDB70-5ED9-49F7-8193-D65789DD43BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -76,49 +89,28 @@
     <t>作者将post-training scaling分为三个主要方法：Supervised Fine-tuning (SFT), Reinforcement Learning (RLxF), and Test-time Compute (TTC).</t>
   </si>
   <si>
-    <t>作者将post-training scaling分为三个主要方法：监督微调（Supervised Fine-tuning）、强化学习（Reinforcement Learning）和测试时计算（Test-time Compute）。
-来自: [2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models, 第2页, 2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models_chunk_002]</t>
-  </si>
-  <si>
     <t>在SafeRAG中"silver noise"的定义是什么？</t>
   </si>
   <si>
     <t>首先，我们定义了“银色噪声”，它指的是仅部分包含答案的证据文本。此类噪声能够绕过大多数安全过滤机制，从而削弱 RAG 的多样性。</t>
   </si>
   <si>
-    <t>Silver noise 是指包含部分但不完整答案的噪声。
-来自: [2025.acl-long.230_SafeRAG, 第3页, 2025.acl-long.230_SafeRAG_chunk_004]</t>
-  </si>
-  <si>
     <t>RAG噪声被分为哪两类？</t>
   </si>
   <si>
     <t>RAG噪声被分为有益噪声和有害噪声。</t>
   </si>
   <si>
-    <t>RAG噪声被分为有益噪声（beneficial noise）和有害噪声（harmful noise）两类。
-来自: [2025.acl-long.250_Pandora s Box or Aladdin s Lamp, 第2页, 2025.acl-long.250_Pandora s Box or Aladdin s Lamp_chunk_001]</t>
-  </si>
-  <si>
     <t>什么是Ref-Long基准？它评估的是长上下文语言模型的什么能力？</t>
   </si>
   <si>
     <t>Ref-Long是一个专门设计用于评估长上下文语言模型（LCLMs）长上下文引用能力的基准。它要求LCLMs不仅要在给定文档中识别特定关键词，还要找出引用该关键词的文档索引，而不是其他相关但不匹配的文档。</t>
   </si>
   <si>
-    <t>Ref-Long是一个评估长上下文语言模型（LCLMs）长上下文引用能力的基准，要求模型不仅从长上下文中检索特定键，还要识别所有引用该键的文档索引。
-来自: [2025.acl-long.1162_Ref-Long, 第1页, 2025.acl-long.1162_Ref-Long_chunk_000]
-来自: [2025.acl-long.1162_Ref-Long, 第2页, 2025.acl-long.1162_Ref-Long_chunk_001]</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 什么是SYNQA方法？</t>
   </si>
   <si>
     <t>SYNQA 是一种生成式上下文归因数据合成方法。核心思路是：给定选定的上下文句子，由大语言模型（LLM）生成完全受这些句子支持的问题-答案对（QA对）。该方法能够产生反映真实世界多样化问答场景的训练数据，帮助模型学习稳健的归因能力。SYNQA 同时生成以实体为中心和以对话为中心的样本，从而提升模型在不同上下文和领域的泛化能力。</t>
-  </si>
-  <si>
-    <t>SYNQA是一种生成式方法，通过使用维基百科句子并提示大型语言模型生成完全由这些句子支持的问题-答案对，来合成上下文归因训练数据。
-来自: [2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第2页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_001]</t>
   </si>
   <si>
     <t>什么是Agentic Long-Context Understanding (AgenticLU)框架？</t>
@@ -128,70 +120,42 @@
 </t>
   </si>
   <si>
-    <t>AgenticLU是一个旨在通过将有针对性的自我澄清与上下文基础整合到智能体工作流中，来增强大型语言模型对复杂长上下文问题理解的框架。
-来自: [2025.acl-long.275_Self-Taught Agentic Long Context Understanding, 第1页, 2025.acl-long.275_Self-Taught Agentic Long Context Understanding_chunk_000]</t>
-  </si>
-  <si>
     <t>什么是Agentic Reasoning框架?</t>
   </si>
   <si>
     <t>Agentic Reasoning是一个通过集成外部工具使用代理来增强大型语言模型推理的框架。</t>
   </si>
   <si>
-    <t>Agentic Reasoning是一个通过将外部基于LLM的代理作为工具集成到推理过程中来增强推理的框架，允许LLM在推理时将特定任务委托给辅助代理，从而提升整体问题解决能力。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第1页, 2025.acl-long.1383_Agentic Reasoning_chunk_001]</t>
-  </si>
-  <si>
     <t>REAL-MM-RAG 基准测试旨在解决现实世界检索的四个关键属性是什么？</t>
   </si>
   <si>
     <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是：(i) 多模态文档，(ii) 增强的难度，(iii) 真实的RAG查询，(iv) 准确的标注。</t>
   </si>
   <si>
-    <t>REAL-MM-RAG 基准测试旨在解决的四个关键属性是：(i) 多模态文档，(ii) 增强难度，(iii) 现实 RAG 查询，(iv) 准确标注。
-来自: [2025.acl-long.1528_REAL-MM-RAG, 第1页, 2025.acl-long.1528_REAL-MM-RAG_chunk_000]</t>
-  </si>
-  <si>
     <t>ASTUTE RAG的定义是什么？有什么用?</t>
   </si>
   <si>
     <t>为了使大语言模型对不完美的检索结果更具鲁棒性，我们提出了 ASTUTE RAG，这是一种新颖的检索增强生成方法。该方法能够自适应地从大语言模型的内部知识中提取关键信息，在感知信息来源的基础上迭代整合内外部知识，并根据信息的可靠性最终生成答案。</t>
   </si>
   <si>
-    <t>ASTUTE RAG 是一种新颖的检索增强生成（RAG）方法，它自适应地从大语言模型内部知识中提取关键信息，以源感知的方式迭代整合内部与外部知识，并依据信息可靠性确定最终答案。其用途是克服不完美检索增强带来的负面影响，解决大语言模型内部知识与外部检索知识之间的冲突，从而提升 RAG 系统在检索质量不佳甚至最坏情况下的鲁棒性与答案的准确可靠性。
-来自: [2025.acl-long.1476_Astute RAG, 第1页, 2025.acl-long.1476_Astute RAG_chunk_000]；[2025.acl-long.1476_Astute RAG, 第4页, 2025.acl-long.1476_Astute RAG_chunk_004]；[2025.acl-long.1476_Astute RAG, 第2页, 2025.acl-long.1476_Astute RAG_chunk_002]</t>
-  </si>
-  <si>
     <t>L-CiteEval的定义是什么？</t>
   </si>
   <si>
     <t>L-CiteEval是一个开箱即用的评估套件，用于评估长上下文模型（LCMs）的生成质量和保真度。它包含两个关键组件：（1）一个涵盖5大任务类别和11个多样化长上下文任务的综合基准测试，上下文长度从8K到48K；（2）相应的自动评估指标和验证流程，以确保稳健可靠的评估。该套件要求模型生成陈述及其支持证据（引用），从而能够有效区分不同模型在保真度方面的差异。</t>
   </si>
   <si>
-    <t>L-CiteEval 是一个即用型评估套件，用于同时评估长上下文模型在长上下文理解任务中的生成质量和忠实度（fidelity）。
-来自: [2025.acl-long.263_L-CiteEval, 第1页, 2025.acl-long.263_L-CiteEval_chunk_000]</t>
-  </si>
-  <si>
     <t xml:space="preserve"> LongBench v2基准测试包含多少个问题？上下文长度范围是多少？</t>
   </si>
   <si>
     <t>LongBench v2包含503个具有挑战性的多项选择题，上下文长度范围从8,000到200万个单词。</t>
   </si>
   <si>
-    <t>LongBench v2 包含 503 个问题，上下文长度范围从 8k 到 2M 词。
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_000]</t>
-  </si>
-  <si>
     <t>RHIO框架的三个主要组成部分是什么？</t>
   </si>
   <si>
     <t>RHIO框架包含三个主要组件：1.不忠实数据增强, 2.忠实度感知调优, 3.自诱导解码</t>
   </si>
   <si>
-    <t>RHIO框架的三个主要组成部分是：不忠实数据增强（unfaithful data augmentation）、忠实性感知调优（faithfulness-aware tuning）和自诱导解码（self-induced decoding）。
-来自: [2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第14页, 2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_014]</t>
-  </si>
-  <si>
     <t>在How to Train Long-Context Language Models中的监督微调（SFT）阶段，论文作者发现使用哪种类型的数据集能够在长上下文任务上取得最佳性能？</t>
   </si>
   <si>
@@ -199,11 +163,6 @@
   </si>
   <si>
     <t>作者发现，仅使用标准的、短上下文的指令数据集（如 UltraChat）进行微调，就能在长上下文任务上取得最佳效果。</t>
-  </si>
-  <si>
-    <t>论文作者发现，在监督微调（SFT）阶段，仅使用短上下文指令数据集（特别是UltraChat）就能在长上下文任务上取得最佳性能，而添加合成数据反而会损害性能。
-来自: [2025.acl-long.366_How to Train Long-Context Language Models (Effectively), 第6页, 2025.acl-long.366_How to Train Long-Context Language Models (Effectively)_chunk_007]
-来自: [2025.acl-long.366_How to Train Long-Context Language Models (Effectively), 第5页, 2025.acl-long.366_How to Train Long-Context Language Models (Effectively)_chunk_006]</t>
   </si>
   <si>
     <t>在"Astute RAG"中，作者提出的knowledge consolidation过程包含哪三个主要步骤？</t>
@@ -215,38 +174,22 @@
 过滤无关信息：剔除与当前查询或任务不相关的冗余内容。</t>
   </si>
   <si>
-    <t>ASTUTE RAG 的三个主要步骤为：自适应生成内部知识（adaptive generation of internal knowledge）、源感知知识整合（source-aware knowledge consolidation）和答案最终确定（answer finalization）。
-来自: [2025.acl-long.1476_Astute RAG, 第4页, 2025.acl-long.1476_Astute RAG_chunk_004]</t>
-  </si>
-  <si>
     <t>LongRefiner 在推理时如何降低在线延迟？</t>
   </si>
   <si>
     <t>将推理分为离线阶段和在线阶段。离线阶段完成文档结构化任务，在线阶段仅处理用户查询分析和自适应精炼（输入输出仅数百个 tokens），整体延迟约为标准设置的 25%。</t>
   </si>
   <si>
-    <t>LongRefiner 通过将推理过程分为离线阶段和在线阶段来降低在线延迟：离线阶段预先执行文档结构化任务，在线阶段仅处理查询分析和自适应精炼，从而大幅减少在线处理时间。
-来自: [2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation, 第6页, 2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation_chunk_006]</t>
-  </si>
-  <si>
     <t>DRAG框架如何保护用户隐私？请描述其隐私保护机制。</t>
   </si>
   <si>
     <t>DRAG通过传输去标识化的查询和结构化知识而不是完整响应来保护用户隐私。这样可以避免传输完整的用户查询和敏感信息。</t>
   </si>
   <si>
-    <t>DRAG框架通过本地学生模型（SLM）对用户查询进行隐私过滤，再与云端大模型交互，从而保护用户隐私。具体机制是：本地SLM首先重新表述原始查询，剥离其中的敏感信息（如个人身份信息），然后将这个去标识化的查询发送给云端大模型。云端大模型仅基于此查询生成相关证据和知识图谱，并返回给本地SLM。最终，本地SLM利用这些结构化知识生成最终答案，确保用户的原始隐私数据不会离开本地设备。
-来自: [2025.acl-long.358_DRAG, 第4页, 2025.acl-long.358_DRAG_chunk_004]</t>
-  </si>
-  <si>
     <t>简述 Think&amp; Cite 框架中 SG-MCTS 的工作流程及其步骤。</t>
   </si>
   <si>
     <t>SG-MCTS利用LLMs的自反思能力来推理MCTS的中间状态，以指导树扩展过程。在每次迭代中，SG-MCTS 遵循四个步骤，即选择、反思引导的扩展、评估和反向传播。</t>
-  </si>
-  <si>
-    <t>SG-MCTS 的工作流程每轮迭代包含四个步骤：选择、反思引导的扩展、评估和反向传播。选择阶段利用 UCT 算法从搜索树中选出最优节点；反思引导的扩展阶段通过“思考-表达-引用”过程生成后继节点，并引入反思步骤对初始查询进行批评和修正，以检索更相关的证据；评估阶段使用进度奖励模型从生成质量和归因一致性两方面计算节点奖励；反向传播阶段将奖励向上更新路径上各节点的统计值。
-来自: [2025.acl-long.490_Think&amp;Cite, 第3页, 2025.acl-long.490_Think&amp;Cite_chunk_002] 和 [2025.acl-long.490_Think&amp;Cite, 第4页, 2025.acl-long.490_Think&amp;Cite_chunk_003]</t>
   </si>
   <si>
     <t>SETR 的段落选择提示（Passage Selection Prompt）所引导的关键过程包含哪三个具体步骤？每个步骤的核心任务是什么？</t>
@@ -258,215 +201,399 @@
 选择最优段落子集： 核心任务是从候选段落中挑选出一个子集，使其在整体上能提供最全面且多样化的信息覆盖，从而有效回答查询。</t>
   </si>
   <si>
+    <t>Meta-Bench基准测试中，α参数的最优范围是多少？这个参数的作用是什么？</t>
+  </si>
+  <si>
+    <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重。</t>
+  </si>
+  <si>
+    <t>根据已有信息，无法回答此问题。</t>
+  </si>
+  <si>
+    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
+  </si>
+  <si>
+    <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ClinRaGen框架的三阶段理由蒸馏范式是什么？</t>
+  </si>
+  <si>
+    <t>ClinRaGen框架采用三阶段理由蒸馏范式：第一阶段从医疗笔记中蒸馏理由，让SLM发展对文本临床信息的基础理解；第二阶段引入知识增强注意力，将数值实验室测试与结构化医学知识对齐，蒸馏实验室测试为基础的理由；第三阶段完全整合文本和数值输入，使SLM能够生成临床连贯的多模态理由以支持疾病诊断。</t>
+  </si>
+  <si>
+    <t>QAEncoder如何解决文档-查询差距问题？</t>
+  </si>
+  <si>
+    <t>QAEncoder采用了一种无需训练的方法来弥合文档与查询之间的差距。其核心机制包含两点：
+潜在查询期望估计： 在嵌入空间中估计潜在查询的期望值，将其作为文档嵌入的鲁棒替代表示，从而使文档表示在语义上更贴近查询空间。
+文档指纹附加： 为这些嵌入表示附加文档指纹，以有效区分不同文档的嵌入，避免仅依赖查询期望导致的文档辨识度丢失问题。</t>
+  </si>
+  <si>
+    <t>在 HALOGEN 的文本简化任务中，如何验证模型生成的简化文本是否忠实于原文？</t>
+  </si>
+  <si>
+    <t>先用 GPT-3.5-turbo 将简化文本分解为独立的原子事实，再用 Llama-2-70B-chat 判断每个原子事实是否被原文蕴含。</t>
+  </si>
+  <si>
+    <t>在"CiteEval"论文中，GPT-4o和Llama-3-70B在Cited scenario和Full scenario下的表现有何差异？</t>
+  </si>
+  <si>
+    <t>实验结果类</t>
+  </si>
+  <si>
+    <t>在Cited scenario下，GPT-4o表现最佳，Llama-3-70B与GPT-4o-mini相当；在Full scenario下，Llama-3-70B超越GPT-4o，取得最佳性能。</t>
+  </si>
+  <si>
+    <t>"FaithfulRAG"在FaithEval数据集上使用Mistral-7B作为backbone时的准确率是多少？相比最强基线提高了多少？</t>
+  </si>
+  <si>
+    <t>81.7%，比最强基线(KRE的73.2%)提高了8.5%。</t>
+  </si>
+  <si>
+    <t>RankCoT 相对于 vanilla RAG 模型的表现如何？这说明了什么？</t>
+  </si>
+  <si>
+    <t>RankCoT 相比 vanilla RAG 模型有 2.5% 的提升，表明它在提供更有意义的细化方面有效，有助于 LLM 更好地回答问题。</t>
+  </si>
+  <si>
+    <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是多少？</t>
+  </si>
+  <si>
+    <t>实验发现，即使是表现最好的 LLM，其生成事实的幻觉率也在 3% 到 86% 之间，具体数值取决于所属领域。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 在LongBench v2基准测试中，人类专家在15分钟时间限制下的准确率是多少？</t>
+  </si>
+  <si>
+    <t>人类专家在15分钟时间限制下的准确率为53.7%。</t>
+  </si>
+  <si>
+    <t>AGENTSTAR方法在WebShop、ALFWorld和BabyAI任务上与GPT-4-Turbo相比有何优势？</t>
+  </si>
+  <si>
+    <t>AGENTSTAR 在这三个任务上的性能全面超越了 GPT-4-Turbo。其中在 WebShop 上的提升最为显著（远超 GPT-4-Turbo 61 个百分点），在 ALFWorld 和 BabyAI 上也分别实现了大幅领先（超过 GPT-4-Turbo 20.5 和 9.87 个百分点）。</t>
+  </si>
+  <si>
+    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合的性能提升是多少？与OpenAI Deep Research的差距如何变化？</t>
+  </si>
+  <si>
+    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合达到了23.8%的准确率，比基础模型提升了14.4%，与专有的OpenAI Deep Research的差距缩小到仅2.8%。</t>
+  </si>
+  <si>
+    <t>在GAIA基准测试中，Agentic Reasoning在不同级别任务上的表现如何？</t>
+  </si>
+  <si>
+    <t>在GAIA基准测试中，Agentic Reasoning在Level 1和Level 2任务上超越了OpenAI的Deep Research，在Level 3任务上将差距缩小到2.26%。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 在Asclepius医学基准测试中，人类医生与Med-MLLMs的表现对比如何？</t>
+  </si>
+  <si>
+    <t>在Asclepius基准测试中，人类医生在所有专业领域都超过了Med-MLLMs。即使是平均准确率为57.4%的初级医生也略微超过了表现最好的Med-MLLM GPT-4V（准确率为54.3%）。这表明尽管人工智能取得了进步，但在诊断精度方面人类专业知识与当前Med-MLLMs之间仍存在差距。</t>
+  </si>
+  <si>
+    <t>在LongDocURL基准测试中，GPT-4o的表现如何？其他开源模型呢？</t>
+  </si>
+  <si>
+    <t>在LongDocURL基准测试中，只有GPT-4o达到了及格标准，得分为64.5，表明该基准对当前模型提出了重大挑战。在开源模型中，只有Qwen2-VL（得分30.6）和LLaVA-OneVision（得分22.0和25.0）超过了20分的阈值，其他参数少于13B的模型都低于这个阈值。</t>
+  </si>
+  <si>
+    <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
+  </si>
+  <si>
+    <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%。</t>
+  </si>
+  <si>
+    <t>在利用大模型内部知识应对知识冲突时，《Astute RAG》与《FaithfulRAG》各自采用了什么核心机制/模块来提取或生成内部知识？</t>
+  </si>
+  <si>
+    <t>跨论文比较类</t>
+  </si>
+  <si>
+    <t>《Astute RAG》：采用自适应段落生成机制，通过提示大模型直接生成包含内部知识的段落，并允许模型自适应决定生成的段落数量。
+《FaithfulRAG》：采用自我事实挖掘 模块，通过外部化大模型对问题的理解，提取出细粒度的、事实级别的内部知识。</t>
+  </si>
+  <si>
+    <t>"UniRAG"和"FaithfulRAG"在处理查询理解方面的核心创新分别是什么？</t>
+  </si>
+  <si>
+    <t>UniRAG提出统一的查询理解框架，集成查询增强和查询编码两个阶段；FaithfulRAG通过自我事实挖掘和自思考模块，在事实级别识别并解决参数化知识与检索上下文之间的冲突，提高语义一致性。</t>
+  </si>
+  <si>
+    <t>比较MEMERAG和DragonBall两个基准的异同点，它们各自关注的评估维度是什么？</t>
+  </si>
+  <si>
+    <t>相同点：两者都是多语言RAG评估基准。不同点：MEMERAG专注于多语言端到端元评估，使用母语问题并由专家评估忠实度和相关性；DragonBall是一个多场景多语言RAG全能基准，涵盖金融、法律、医疗领域，包含6,711个问题，用于评估RAG系统在不同场景下的性能。</t>
+  </si>
+  <si>
+    <t>SYNQA 和 RHIO 分别通过什么方式生成训练数据？这两种数据生成策略在提升模型归因能力上有什么不同？</t>
+  </si>
+  <si>
+    <t>SYNQA：通过 LLM 生成式合成完全受上下文支持的 QA 对（正样本），用于微调小模型的归因能力。
+RHIO：通过选择性掩码检索头，让 LLM 自身生成模拟真实错误的不忠实样本（负样本），并与忠实样本进行联合训练。</t>
+  </si>
+  <si>
+    <t>比较LongBench v2和AGENTGYM应用场景区别。</t>
+  </si>
+  <si>
+    <t>LongBench v2：专注于长上下文理解的多任务评估，包含503个多项选择题，上下文长度从8k到2M单词，涵盖6个主要任务类别，用于评估LLM在长文档理解和推理方面的能力
+AGENTGYM：专注于代理训练和工具使用的环境集合，包含11个不同的交互环境（如Minecraft、ScienceWorld、BabyAI等），用于训练和评估LLM代理在多样化任务中的能力</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning 与 AR-MCTS 分别采用什么核心机制来提升复杂推理能力？</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning：动态调用网页搜索、代码执行作为工具，并引入 Mind‑Map 知识图谱智能体作为结构化记忆，存储推理上下文并追踪逻辑关系。
+AR-MCTS：基于蒙特卡洛树搜索（MCTS），在扩展阶段集成主动检索（Active Retrieval） 机制，自动获取逐步推理的高质量标注，渐进式提升多模态大模型的推理能力。</t>
+  </si>
+  <si>
+    <t>MAIN‑RAG 与 RAG‑Critic 在提升 RAG 系统可靠性方面分别采用了什么核心方法？</t>
+  </si>
+  <si>
+    <t>MAIN‑RAG 采用多智能体协作过滤机制，通过三个 LLM 智能体（Predictor、Judge、Final‑Predictor）对检索文档进行相关性评分和排序，并利用自适应阈值动态过滤噪声文档，无需训练。
+RAG‑Critic 采用批评引导的智能体工作流，首先构建层次化 RAG 错误系统（3 级错误类型，含 4000+ 细粒度标签），然后训练轻量级错误批评模型进行自动错误诊断，最后通过规划智能体根据错误反馈定制并执行修正方案。</t>
+  </si>
+  <si>
+    <t>在构建可靠的问答（QA）系统时，这QAEncoder与On Synthesizing Data for Context Attribution in Question Answering两篇论文分别侧重于优化系统工作流的哪个阶段？它们各自试图解决的核心痛点是什么？</t>
+  </si>
+  <si>
+    <t>《QAEncoder》侧重于“检索阶段”
+核心痛点：用户的自然语言查询与知识库中的文档之间存在语义和词汇上的鸿沟，导致检索模块无法精准召回相关文档。
+《On Synthesizing Data for Context Attribution... (SYNQA)》侧重于“生成后阶段”
+核心痛点：大语言模型在生成答案时容易产生幻觉，用户很难验证生成的答案是否真的基于提供的上下文，缺乏可解释性和事实依据。</t>
+  </si>
+  <si>
+    <t>这10篇论文中哪一篇提出了名为"RAG-Guard"的安全防护框架？</t>
+  </si>
+  <si>
+    <t>不可回答类</t>
+  </si>
+  <si>
+    <t>无法回答。</t>
+  </si>
+  <si>
+    <t>"ProLong"模型在训练过程中使用了哪种具体的优化器来处理长序列训练的梯度问题？</t>
+  </si>
+  <si>
+    <t>SETR模型在训练时具体的训练时间是多少小时？</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> L-CiteEval基准中使用的NLI模型deberta-base-long-nli的准确率是多少？该模型在哪些具体数据集上进行了训练？</t>
+  </si>
+  <si>
+    <t>论文中是否提到了SYNQA方法在医疗领域的具体应用案例？</t>
+  </si>
+  <si>
+    <t>论文中是否提供了RHIO方法在实时应用场景中的延迟测试数据？</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning框架中使用的Mind-Map agent的具体神经网络架构是什么？</t>
+  </si>
+  <si>
+    <t>在CypherBench基准测试中，每个问题模板具体包含多少个训练样本？</t>
+  </si>
+  <si>
+    <t>【总体平均值】</t>
+  </si>
+  <si>
+    <t>【定义类平均值】</t>
+  </si>
+  <si>
+    <t>【方法细节类平均值】</t>
+  </si>
+  <si>
+    <t>【实验结果类平均值】</t>
+  </si>
+  <si>
+    <t>【跨论文比较类平均值】</t>
+  </si>
+  <si>
+    <t>【不可回答类平均值】</t>
+  </si>
+  <si>
+    <t>作者将post-training scaling分为三个主要方法：监督微调（Supervised Fine-tuning）、强化学习（Reinforcement Learning）和测试时计算（Test-time Compute）。
+来自: [A Survey of Post-Training Scaling in Large Language Models, 第2页, A Survey of Post-Training Scaling in Large Language Models_chunk_002]</t>
+  </si>
+  <si>
+    <t>Silver noise 是指包含部分但不完整答案的噪声。
+来自: [SafeRAG: Benchmarking Security in Retrieval-Augmented Generation of Large Language Model, 第3页, SafeRAG: Benchmarking Security in Retrieval-Augmented Generation of Large Language Model_chunk_004]</t>
+  </si>
+  <si>
+    <t>RAG噪声被分为有益噪声（beneficial noise）和有害噪声（harmful noise）两类。
+来自: [Pandora’s Box or Aladdin’s Lamp: A Comprehensive Analysis Revealing the Role of RAG Noise in Large Language Models, 第2页, Pandora’s Box or Aladdin’s Lamp: A Comprehensive Analysis Revealing the Role of RAG Noise in Large Language Models_chunk_001]</t>
+  </si>
+  <si>
+    <t>Ref-Long是一个评估长上下文语言模型（LCLMs）长上下文引用能力的基准，要求模型不仅从长上下文中检索特定键，还要识别所有引用该键的文档索引。
+来自: [Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models, 第1页, Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models_chunk_000]
+来自: [Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models, 第2页, Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models_chunk_001]</t>
+  </si>
+  <si>
+    <t>SYNQA是一种生成式方法，通过使用维基百科句子并提示大型语言模型生成完全由这些句子支持的问题-答案对，来合成上下文归因训练数据。
+来自: [On Synthesizing Data for Context Attribution in Question Answering, 第2页, On Synthesizing Data for Context Attribution in Question Answering_chunk_001]</t>
+  </si>
+  <si>
+    <t>AgenticLU是一个旨在通过将有针对性的自我澄清与上下文基础整合到智能体工作流中，来增强大型语言模型对复杂长上下文问题理解的框架。
+来自: [Self-Taught Agentic Long-Context Understanding, 第1页, Self-Taught Agentic Long-Context Understanding_chunk_000]</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning是一个通过将外部基于LLM的代理作为工具集成到推理过程中来增强推理的框架，允许LLM在推理时将特定任务委托给辅助代理，从而提升整体问题解决能力。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第1页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_001]</t>
+  </si>
+  <si>
+    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合后，准确率从9.4%提升至23.8%，提升了14.4个百分点；与OpenAI Deep Research的差距从17.2%缩小至2.8%。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第1页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_000]</t>
+  </si>
+  <si>
+    <t>在GAIA基准测试中，Agentic Reasoning在Level 1上的得分为74.36，Level 2为69.21，Level 3为45.46，平均分为66.13。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第5页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_004]</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning 的核心机制是集成外部基于LLM的代理工具（如网页搜索、代码执行和思维导图代理）来增强推理能力。AR-MCTS 的核心机制则是通过主动检索（Active Retrieval）和蒙特卡洛树搜索（MCTS）来逐步提升多模态推理能力。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第1页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_001] 和 [2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval, 第1页, 2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval_chunk_000]</t>
+  </si>
+  <si>
+    <t>根据已有信息，论文仅指出Mind-Map agent的实现是基于DeepSeek-V3大语言模型来执行知识图谱构建和检索，但并未披露其具体的神经网络架构细节。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第2页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_002] 和 [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第5页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_004]</t>
+  </si>
+  <si>
+    <t>REAL-MM-RAG 基准测试旨在解决的四个关键属性是：(i) 多模态文档，(ii) 增强难度，(iii) 现实 RAG 查询，(iv) 准确标注。
+来自: [REAL-MM-RAG:AReal-World Multi-Modal Retrieval Benchmark, 第1页, REAL-MM-RAG:AReal-World Multi-Modal Retrieval Benchmark_chunk_000]</t>
+  </si>
+  <si>
+    <t>ASTUTE RAG 是一种新颖的检索增强生成（RAG）方法，它自适应地从大语言模型内部知识中提取关键信息，以源感知的方式迭代整合内部与外部知识，并依据信息可靠性确定最终答案。其用途是克服不完美检索增强带来的负面影响，解决大语言模型内部知识与外部检索知识之间的冲突，从而提升 RAG 系统在检索质量不佳甚至最坏情况下的鲁棒性与答案的准确可靠性。
+来自: [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第1页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_000]；[ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第4页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_004]；[ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第2页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_002]</t>
+  </si>
+  <si>
+    <t>ASTUTE RAG 的三个主要步骤为：自适应生成内部知识（adaptive generation of internal knowledge）、源感知知识整合（source-aware knowledge consolidation）和答案最终确定（answer finalization）。
+来自: [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第4页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_004]</t>
+  </si>
+  <si>
+    <t>L-CiteEval 是一个即用型评估套件，用于同时评估长上下文模型在长上下文理解任务中的生成质量和忠实度（fidelity）。
+来自: [L-CiteEval: A Suite for Evaluating Fidelity of Long-context Models, 第1页, L-CiteEval: A Suite for Evaluating Fidelity of Long-context Models_chunk_000]</t>
+  </si>
+  <si>
+    <t>LongBench v2 包含 503 个问题，上下文长度范围从 8k 到 2M 词。
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_000]</t>
+  </si>
+  <si>
+    <t>人类专家在15分钟时间限制下的准确率为53.7%。
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_000]</t>
+  </si>
+  <si>
+    <t>RHIO框架的三个主要组成部分是：不忠实数据增强（unfaithful data augmentation）、忠实性感知调优（faithfulness-aware tuning）和自诱导解码（self-induced decoding）。
+来自: [Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第14页, Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_014]</t>
+  </si>
+  <si>
+    <t>SYNQA 通过生成式方法合成训练数据：从 Wikipedia 选取上下文句子，让大语言模型（Llama 70B）生成完全由这些句子支持的问答对，并加入语义相似的干扰文章，从而确保每条数据都有清晰的归因路径。RHIO 则通过遮蔽检索头来生成不忠实样本，模拟模型内在的错误类型，然后将这些不忠实样本与忠实样本一起用于训练，使模型学会区分忠实与不忠实的输出。
+在提升归因能力上，两者的策略不同：SYNQA 直接训练一个专门的上下文归因模型，使其能够精确识别支持答案的句子，从而在句子级归因任务上提升精确度和召回率，让小模型甚至超越大模型；RHIO 并不直接做归因，而是通过增强模型对上下文忠实性的感知，在生成过程中抑制不忠实内容，从而提升生成结果的上下文忠实度。
+来自: [On Synthesizing Data for Context Attribution in Question Answering, 第2页, On Synthesizing Data for Context Attribution in Question Answering_chunk_002]、[On Synthesizing Data for Context Attribution in Question Answering, 第2页, On Synthesizing Data for Context Attribution in Question Answering_chunk_001]、[Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第1页, Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_000]、[Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第7页, Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_008]</t>
+  </si>
+  <si>
+    <t>论文作者发现，在监督微调（SFT）阶段，仅使用短上下文指令数据集（特别是UltraChat）就能在长上下文任务上取得最佳性能，而添加合成数据反而会损害性能。
+来自: How to Train Long-Context Language Models (Effectively), 第6页, 2025.acl-long.366_How to Train Long-Context Language Models (Effectively)_chunk_007]
+来自: How to Train Long-Context Language Models (Effectively), 第5页, 2025.acl-long.366_How to Train Long-Context Language Models (Effectively)_chunk_006]</t>
+  </si>
+  <si>
+    <t>ProLong模型在训练过程中使用的优化器是AdamW。
+来自: How to Train Long-Context Language Models (Effectively), 第13页, 2025.acl-long.366_How to Train Long-Context Language Models (Effectively)_chunk_013]</t>
+  </si>
+  <si>
+    <t>LongRefiner 通过将推理过程分为离线阶段和在线阶段来降低在线延迟：离线阶段预先执行文档结构化任务，在线阶段仅处理查询分析和自适应精炼，从而大幅减少在线处理时间。
+来自: [Hierarchical Document Refinement for Long-context Retrieval-augmented Generation, 第6页, Hierarchical Document Refinement for Long-context Retrieval-augmented Generation_chunk_006]</t>
+  </si>
+  <si>
+    <t>DRAG框架通过本地学生模型（SLM）对用户查询进行隐私过滤，再与云端大模型交互，从而保护用户隐私。具体机制是：本地SLM首先重新表述原始查询，剥离其中的敏感信息（如个人身份信息），然后将这个去标识化的查询发送给云端大模型。云端大模型仅基于此查询生成相关证据和知识图谱，并返回给本地SLM。最终，本地SLM利用这些结构化知识生成最终答案，确保用户的原始隐私数据不会离开本地设备。
+来自: [DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation, 第4页, DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation_chunk_004]</t>
+  </si>
+  <si>
+    <t>SG-MCTS 的工作流程每轮迭代包含四个步骤：选择、反思引导的扩展、评估和反向传播。选择阶段利用 UCT 算法从搜索树中选出最优节点；反思引导的扩展阶段通过“思考-表达-引用”过程生成后继节点，并引入反思步骤对初始查询进行批评和修正，以检索更相关的证据；评估阶段使用进度奖励模型从生成质量和归因一致性两方面计算节点奖励；反向传播阶段将奖励向上更新路径上各节点的统计值。
+来自: [Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling, 第3页, Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling_chunk_002] 和 [Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling, 第4页, Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling_chunk_003]</t>
+  </si>
+  <si>
     <t>SETR 的段落选择提示引导的关键过程包含以下三个步骤：
 1.  **列举信息需求**：分解输入问题，列出回答该问题所需的关键信息需求。
 2.  **匹配相关段落**：针对第一步中的每个信息需求，找出包含相关信息的候选段落。
 3.  **选择最优子集**：从候选段落中选择一个子集，该子集能共同提供最全面、最多样化的信息覆盖，以有效回答查询。
-来自: [2025.acl-long.861_Shifting from Ranking to Set Selection for Retrieval Augmented Generation, 第3页, 2025.acl-long.861_Shifting from Ranking to Set Selection for Retrieval Augmented Generation_chunk_003]</t>
-  </si>
-  <si>
-    <t>Meta-Bench基准测试中，α参数的最优范围是多少？这个参数的作用是什么？</t>
-  </si>
-  <si>
-    <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重。</t>
-  </si>
-  <si>
-    <t>根据已有信息，无法回答此问题。</t>
-  </si>
-  <si>
-    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
-  </si>
-  <si>
-    <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
+来自: [Shifting from Ranking to Set Selection for Retrieval Augmented Generation, 第3页, Shifting from Ranking to Set Selection for Retrieval Augmented Generation_chunk_003]</t>
   </si>
   <si>
     <t>CypherBench 通过两个主要步骤从 RDF 图生成领域特定的属性图：  
 1. **手动策划领域模式**：针对选定领域，人工定义属性图的模式（包括实体类型、关系类型及其属性），并建立从 Wikidata 标识符（QID 和 PID）到该模式的映射。  
 2. **自动 RDF‑到‑属性图转换**：转换引擎根据策划的模式向 Wikidata 发出 SPARQL 查询，获取所有符合模式的实体和关系，并执行数据类型转换、单位标准化和排名过滤，最终输出模式强制、类型严格的属性图。
-来自: [2025.acl-long.438_CypherBench, 第4页, 2025.acl-long.438_CypherBench_chunk_004]  
-来自: [2025.acl-long.438_CypherBench, 第3页, 2025.acl-long.438_CypherBench_chunk_003]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ClinRaGen框架的三阶段理由蒸馏范式是什么？</t>
-  </si>
-  <si>
-    <t>ClinRaGen框架采用三阶段理由蒸馏范式：第一阶段从医疗笔记中蒸馏理由，让SLM发展对文本临床信息的基础理解；第二阶段引入知识增强注意力，将数值实验室测试与结构化医学知识对齐，蒸馏实验室测试为基础的理由；第三阶段完全整合文本和数值输入，使SLM能够生成临床连贯的多模态理由以支持疾病诊断。</t>
+来自: [CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era, 第4页, CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era_chunk_004]  
+来自: [CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era, 第3页, CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era_chunk_003]</t>
   </si>
   <si>
     <t>ClinRaGen的三阶段理由蒸馏范式是一个逐步整合文本、数值和结构化领域知识的过程：第一阶段仅基于医疗笔记训练小语言模型，使其生成诊断和基于笔记的理由；第二阶段引入知识增强注意力模块，将数值化实验室检测数据与结构化医学知识对齐，以蒸馏基于实验室检测的理由；第三阶段完全整合文本和数值输入，使模型生成临床连贯的多模态理由。
-来自: [2025.acl-long.540_Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models, 第3页, 2025.acl-long.540_Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models_chunk_003]
-来自: [2025.acl-long.540_Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models, 第4页, 2025.acl-long.540_Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models_chunk_004]</t>
-  </si>
-  <si>
-    <t>QAEncoder如何解决文档-查询差距问题？</t>
-  </si>
-  <si>
-    <t>QAEncoder采用了一种无需训练的方法来弥合文档与查询之间的差距。其核心机制包含两点：
-潜在查询期望估计： 在嵌入空间中估计潜在查询的期望值，将其作为文档嵌入的鲁棒替代表示，从而使文档表示在语义上更贴近查询空间。
-文档指纹附加： 为这些嵌入表示附加文档指纹，以有效区分不同文档的嵌入，避免仅依赖查询期望导致的文档辨识度丢失问题。</t>
+来自: [Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models, 第3页, Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models_chunk_003]
+来自: [Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models, 第4页, Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models_chunk_004]</t>
   </si>
   <si>
     <t>QAEncoder通过两个核心机制解决文档-查询差距：首先，它用潜在查询在嵌入空间中的期望（聚类中心）作为文档嵌入的鲁棒替代，从而在语义上对齐查询和文档；其次，它引入文档指纹策略，将文档的独特身份重新注入表示中，以保持文档间的区分度。
-来自: [2025.acl-long.217_QAEncoder, 第1页, 2025.acl-long.217_QAEncoder_chunk_000]、[2025.acl-long.217_QAEncoder, 第3页, 2025.acl-long.217_QAEncoder_chunk_003]、[2025.acl-long.217_QAEncoder, 第4页, 2025.acl-long.217_QAEncoder_chunk_004]</t>
-  </si>
-  <si>
-    <t>在 HALOGEN 的文本简化任务中，如何验证模型生成的简化文本是否忠实于原文？</t>
-  </si>
-  <si>
-    <t>先用 GPT-3.5-turbo 将简化文本分解为独立的原子事实，再用 Llama-2-70B-chat 判断每个原子事实是否被原文蕴含。</t>
+来自: [QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第1页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_000]、[QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第3页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_003]、[QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第4页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_004]</t>
+  </si>
+  <si>
+    <t>QAEncoder侧重于优化QA系统的**检索阶段**，其核心痛点是**文档与用户查询之间的语义鸿沟（document-query gap）**，即文档表示与查询表示不匹配导致难以精准检索到相关文档。
+来自: [QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第1页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_000]
+On Synthesizing Data for Context Attribution in Question Answering侧重于优化QA系统的**生成后验证/归因阶段**，其核心痛点是**大语言模型（LLM）的幻觉问题**，即生成的答案可能缺乏事实依据，需要将答案内容归因到上下文中的具体证据，以提升可信度。
+来自: [On Synthesizing Data for Context Attribution in Question Answering, 第1页, On Synthesizing Data for Context Attribution in Question Answering_chunk_000]</t>
   </si>
   <si>
     <t>在 HALOGEN 的文本简化任务中，验证生成文本忠实性的方法与摘要任务相同：首先使用 GPT-3.5 将模型生成的简化文本分解为独立的原子事实，然后使用 Llama-2-70B 对每个原子事实进行蕴含判断，以确定其是否被原文支持。
-来自: [2025.acl-long.71_HALoGEN, 第3页, 2025.acl-long.71_HALoGEN_chunk_003] 和 [2025.acl-long.71_HALoGEN, 第4页, 2025.acl-long.71_HALoGEN_chunk_004]</t>
-  </si>
-  <si>
-    <t>在"CiteEval"论文中，GPT-4o和Llama-3-70B在Cited scenario和Full scenario下的表现有何差异？</t>
-  </si>
-  <si>
-    <t>实验结果类</t>
-  </si>
-  <si>
-    <t>在Cited scenario下，GPT-4o表现最佳，Llama-3-70B与GPT-4o-mini相当；在Full scenario下，Llama-3-70B超越GPT-4o，取得最佳性能。</t>
+来自: [HALOGEN :FantasticLLMHallucinations and Where to Find Them, 第3页, HALOGEN :FantasticLLMHallucinations and Where to Find Them_chunk_003] 和 [HALOGEN :FantasticLLMHallucinations and Where to Find Them, 第4页, HALOGEN :FantasticLLMHallucinations and Where to Find Them_chunk_004]</t>
+  </si>
+  <si>
+    <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是 3% 到 86%，具体取决于领域。
+来自: [HALOGEN :FantasticLLMHallucinations and Where to Find Them, 第5页, HALOGEN :FantasticLLMHallucinations and Where to Find Them_chunk_005]</t>
   </si>
   <si>
     <t>在Cited scenario下，GPT-4o的评分（0.949）高于Llama-3-70B（0.926），表现最佳；而在Full scenario下，Llama-3-70B的评分（0.909）反超GPT-4o（0.898），取得了最优性能。
-来自: [2025.acl-long.1574_CiteEval, 第7页, 2025.acl-long.1574_CiteEval_chunk_007] 和 [2025.acl-long.1574_CiteEval, 第7页, 2025.acl-long.1574_CiteEval_chunk_008]</t>
-  </si>
-  <si>
-    <t>"FaithfulRAG"在FaithEval数据集上使用Mistral-7B作为backbone时的准确率是多少？相比最强基线提高了多少？</t>
-  </si>
-  <si>
-    <t>81.7%，比最强基线(KRE的73.2%)提高了8.5%。</t>
+来自: [CiteEval: Principle-Driven Citation Evaluation for Source Attribution, 第7页, CiteEval: Principle-Driven Citation Evaluation for Source Attribution_chunk_007] 和 [CiteEval: Principle-Driven Citation Evaluation for Source Attribution, 第7页, CiteEval: Principle-Driven Citation Evaluation for Source Attribution_chunk_008]</t>
   </si>
   <si>
     <t>FaithfulRAG在FaithEval数据集上使用Mistral-7B作为backbone时的准确率为81.7%，相比最强基线（KRE的73.2%）提高了8.5%。
-来自: [2025.acl-long.1062_FaithfulRAG, 第6页, 2025.acl-long.1062_FaithfulRAG_chunk_007]</t>
-  </si>
-  <si>
-    <t>RankCoT 相对于 vanilla RAG 模型的表现如何？这说明了什么？</t>
-  </si>
-  <si>
-    <t>RankCoT 相比 vanilla RAG 模型有 2.5% 的提升，表明它在提供更有意义的细化方面有效，有助于 LLM 更好地回答问题。</t>
-  </si>
-  <si>
-    <t>RankCoT 相对于 vanilla RAG 模型有显著提升。例如，在使用 Llama3-8B-Instruct 作为骨干模型时，RankCoT 的平均得分比 vanilla RAG 高出约 2.5%（46.93 vs 42.84）；在与更多基线模型比较时，RankCoT 的平均得分也高于 vanilla RAG（54.93 vs 52.65）。这说明 RankCoT 能够提供更有意义的知识精炼，从而帮助大语言模型更好地回答问题。
-来自: [2025.acl-long.629_RankCoT, 第6页, 2025.acl-long.629_RankCoT_chunk_008]
-来自: [2025.acl-long.629_RankCoT, 第12页, 2025.acl-long.629_RankCoT_chunk_012]</t>
-  </si>
-  <si>
-    <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是多少？</t>
-  </si>
-  <si>
-    <t>实验发现，即使是表现最好的 LLM，其生成事实的幻觉率也在 3% 到 86% 之间，具体数值取决于所属领域。</t>
-  </si>
-  <si>
-    <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是 3% 到 86%，具体取决于领域。
-来自: [2025.acl-long.71_HALoGEN, 第5页, 2025.acl-long.71_HALoGEN_chunk_005]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 在LongBench v2基准测试中，人类专家在15分钟时间限制下的准确率是多少？</t>
-  </si>
-  <si>
-    <t>人类专家在15分钟时间限制下的准确率为53.7%。</t>
-  </si>
-  <si>
-    <t>人类专家在15分钟时间限制下的准确率为53.7%。
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_000]</t>
-  </si>
-  <si>
-    <t>AGENTSTAR方法在WebShop、ALFWorld和BabyAI任务上与GPT-4-Turbo相比有何优势？</t>
-  </si>
-  <si>
-    <t>AGENTSTAR 在这三个任务上的性能全面超越了 GPT-4-Turbo。其中在 WebShop 上的提升最为显著（远超 GPT-4-Turbo 61 个百分点），在 ALFWorld 和 BabyAI 上也分别实现了大幅领先（超过 GPT-4-Turbo 20.5 和 9.87 个百分点）。</t>
-  </si>
-  <si>
-    <t>AGENTSTAR在WebShop、ALFWorld和BabyAI任务上均显著优于GPT-4-Turbo，分别高出61.00、20.50和9.87个百分点。
-来自: [2025.acl-long.1355_AgentGym, 第6页, 2025.acl-long.1355_AgentGym_chunk_008]</t>
-  </si>
-  <si>
-    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合的性能提升是多少？与OpenAI Deep Research的差距如何变化？</t>
-  </si>
-  <si>
-    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合达到了23.8%的准确率，比基础模型提升了14.4%，与专有的OpenAI Deep Research的差距缩小到仅2.8%。</t>
-  </si>
-  <si>
-    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合后，准确率从9.4%提升至23.8%，提升了14.4个百分点；与OpenAI Deep Research的差距从17.2%缩小至2.8%。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第1页, 2025.acl-long.1383_Agentic Reasoning_chunk_000]</t>
-  </si>
-  <si>
-    <t>在GAIA基准测试中，Agentic Reasoning在不同级别任务上的表现如何？</t>
-  </si>
-  <si>
-    <t>在GAIA基准测试中，Agentic Reasoning在Level 1和Level 2任务上超越了OpenAI的Deep Research，在Level 3任务上将差距缩小到2.26%。</t>
-  </si>
-  <si>
-    <t>在GAIA基准测试中，Agentic Reasoning在Level 1上的得分为74.36，Level 2为69.21，Level 3为45.46，平均分为66.13。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第5页, 2025.acl-long.1383_Agentic Reasoning_chunk_004]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 在Asclepius医学基准测试中，人类医生与Med-MLLMs的表现对比如何？</t>
-  </si>
-  <si>
-    <t>在Asclepius基准测试中，人类医生在所有专业领域都超过了Med-MLLMs。即使是平均准确率为57.4%的初级医生也略微超过了表现最好的Med-MLLM GPT-4V（准确率为54.3%）。这表明尽管人工智能取得了进步，但在诊断精度方面人类专业知识与当前Med-MLLMs之间仍存在差距。</t>
-  </si>
-  <si>
-    <t>在Asclepius基准测试中，人类医生在所有医学专科的诊断准确率上均优于Med‑MLLMs。即使是一位初级医生，其平均准确率（57.4%）也略高于表现最好的Med‑MLLM GPT‑4V（54.3%）。GPT‑4V的表现最接近人类医生，但仍存在差距。此外，人类医生在不同专科间的表现差异较大，而Med‑MLLMs的表现更为均匀。
-来自: [2025.acl-long.1178_Asclepius, 第7页, 2025.acl-long.1178_Asclepius_chunk_008]
-来自: [2025.acl-long.1178_Asclepius, 第7页, 2025.acl-long.1178_Asclepius_chunk_007]
-来自: [2025.acl-long.1178_Asclepius, 第14页, 2025.acl-long.1178_Asclepius_chunk_011]</t>
-  </si>
-  <si>
-    <t>在LongDocURL基准测试中，GPT-4o的表现如何？其他开源模型呢？</t>
-  </si>
-  <si>
-    <t>在LongDocURL基准测试中，只有GPT-4o达到了及格标准，得分为64.5，表明该基准对当前模型提出了重大挑战。在开源模型中，只有Qwen2-VL（得分30.6）和LLaVA-OneVision（得分22.0和25.0）超过了20分的阈值，其他参数少于13B的模型都低于这个阈值。</t>
-  </si>
-  <si>
-    <t>在LongDocURL基准测试中，GPT-4o是得分最高的模型，达到了64.5分，也是唯一达到及格标准的模型。在开源模型方面，表现最好的是Qwen2-VL，得分为30.6，其次是LLaVA-OneVision（得分22.0和25.0），只有这两款开源模型得分超过了20分。
-来自: [2025.acl-long.57_LongDocURL, 第6页, 2025.acl-long.57_LongDocURL_chunk_006] 和 [2025.acl-long.57_LongDocURL, 第1页, 2025.acl-long.57_LongDocURL_chunk_001]</t>
-  </si>
-  <si>
-    <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
-  </si>
-  <si>
-    <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%。</t>
-  </si>
-  <si>
-    <t>RAGEval 提出的三个自动评估指标（Completeness、Hallucination 和 Irrelevance）与人工评估之间表现出高度一致性。具体而言，Completeness 的 Spearman 相关系数为 0.8536，Pearson 相关系数为 0.8549；Irrelevance 的 Spearman 相关系数为 0.7589，Pearson 相关系数为 0.7568；Hallucination 的 Spearman 相关系数为 0.7983，Pearson 相关系数为 0.7851。所有结果均具有统计显著性（p &lt; 0.0001）。
-来自: [2025.acl-long.418_RAGEval, 第12页, 2025.acl-long.418_RAGEval_chunk_011]</t>
-  </si>
-  <si>
-    <t>在利用大模型内部知识应对知识冲突时，《Astute RAG》与《FaithfulRAG》各自采用了什么核心机制/模块来提取或生成内部知识？</t>
-  </si>
-  <si>
-    <t>跨论文比较类</t>
-  </si>
-  <si>
-    <t>《Astute RAG》：采用自适应段落生成机制，通过提示大模型直接生成包含内部知识的段落，并允许模型自适应决定生成的段落数量。
-《FaithfulRAG》：采用自我事实挖掘 模块，通过外部化大模型对问题的理解，提取出细粒度的、事实级别的内部知识。</t>
+来自: [FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation, 第6页, FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation_chunk_007]</t>
   </si>
   <si>
     <t>FaithfulRAG 通过 **Self-Fact Mining（自我事实挖掘）** 模块提取内部知识，该模块包含自我知识提取、自我上下文生成和自我事实提取三个步骤，将模型的参数化知识外化为细粒度的事实级表示。  
 Astute RAG 则采用 **自适应内部知识生成（adaptive generation of internal knowledge）** 机制，在宪法原则引导下让 LLM 自行决定生成多少条内部段落，以获取准确、相关且无幻觉的内部知识。
-来自: [2025.acl-long.1062_FaithfulRAG, 第3页, 2025.acl-long.1062_FaithfulRAG_chunk_004]  
-来自: [2025.acl-long.1476_Astute RAG, 第5页, 2025.acl-long.1476_Astute RAG_chunk_005]</t>
-  </si>
-  <si>
-    <t>"UniRAG"和"FaithfulRAG"在处理查询理解方面的核心创新分别是什么？</t>
-  </si>
-  <si>
-    <t>UniRAG提出统一的查询理解框架，集成查询增强和查询编码两个阶段；FaithfulRAG通过自我事实挖掘和自思考模块，在事实级别识别并解决参数化知识与检索上下文之间的冲突，提高语义一致性。</t>
+来自: [FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation, 第3页, FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation_chunk_004]  
+来自: [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第5页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_005]</t>
+  </si>
+  <si>
+    <t>RankCoT 相对于 vanilla RAG 模型有显著提升。例如，在使用 Llama3-8B-Instruct 作为骨干模型时，RankCoT 的平均得分比 vanilla RAG 高出约 2.5%（46.93 vs 42.84）；在与更多基线模型比较时，RankCoT 的平均得分也高于 vanilla RAG（54.93 vs 52.65）。这说明 RankCoT 能够提供更有意义的知识精炼，从而帮助大语言模型更好地回答问题。
+来自: [RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts, 第6页, RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts_chunk_008]
+来自: [RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts, 第12页, RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts_chunk_012]</t>
+  </si>
+  <si>
+    <t>AGENTSTAR在WebShop、ALFWorld和BabyAI任务上均显著优于GPT-4-Turbo，分别高出61.00、20.50和9.87个百分点。
+来自: [AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments, 第6页, AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments_chunk_008]</t>
+  </si>
+  <si>
+    <t>LongBench v2的应用场景是评估大语言模型在真实长上下文多任务中深度理解与推理的能力，涵盖单文档问答、多文档问答、长上下文学习等六类任务。AGENTGYM的应用场景则是评估和训练基于大语言模型的智能体，使其在网页导航、文字游戏、家务任务等七种真实世界场景中执行多轮决策任务。简言之，前者聚焦于静态文本的深度理解与推理评估，后者聚焦于动态交互环境中的智能体行为评估与训练。
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_000]
+来自: [AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments, 第1页, AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments_chunk_000]
+来自: [AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments, 第1页, AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments_chunk_001]</t>
+  </si>
+  <si>
+    <t>在Asclepius基准测试中，人类医生在所有医学专科的诊断准确率上均优于Med‑MLLMs。即使是一位初级医生，其平均准确率（57.4%）也略高于表现最好的Med‑MLLM GPT‑4V（54.3%）。GPT‑4V的表现最接近人类医生，但仍存在差距。此外，人类医生在不同专科间的表现差异较大，而Med‑MLLMs的表现更为均匀。
+来自: [Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models, 第7页, Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models_chunk_008]
+来自: [Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models, 第7页, Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models_chunk_007]
+来自: [Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models, 第14页, Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models_chunk_011]</t>
+  </si>
+  <si>
+    <t>在LongDocURL基准测试中，GPT-4o是得分最高的模型，达到了64.5分，也是唯一达到及格标准的模型。在开源模型方面，表现最好的是Qwen2-VL，得分为30.6，其次是LLaVA-OneVision（得分22.0和25.0），只有这两款开源模型得分超过了20分。
+来自: [LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating, 第6页, LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating_chunk_006] 和 [LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating, 第1页, LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating_chunk_001]</t>
+  </si>
+  <si>
+    <t>RAGEval 提出的三个自动评估指标（Completeness、Hallucination 和 Irrelevance）与人工评估之间表现出高度一致性。具体而言，Completeness 的 Spearman 相关系数为 0.8536，Pearson 相关系数为 0.8549；Irrelevance 的 Spearman 相关系数为 0.7589，Pearson 相关系数为 0.7568；Hallucination 的 Spearman 相关系数为 0.7983，Pearson 相关系数为 0.7851。所有结果均具有统计显著性（p &lt; 0.0001）。
+来自: [RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第12页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_011]</t>
   </si>
   <si>
     <t>UniRAG的核心创新在于将查询增强与查询编码统一到一个解码器模型中，消除任务分离，并通过自适应选择最优增强策略（如查询改写、扩展、抽象）来提升检索效果。  
-来自: [2025.acl-long.693_UniRAG, 第1页, 2025.acl-long.693_UniRAG_chunk_000] 和 [2025.acl-long.693_UniRAG, 第1页, 2025.acl-long.693_UniRAG_chunk_001]
+来自: [UniRAG: Unified Query Understanding Method for Retrieval Augmented Generation, 第1页, UniRAG: Unified Query Understanding Method for Retrieval Augmented Generation_chunk_000] 和 [UniRAG: Unified Query Understanding Method for Retrieval Augmented Generation, 第1页, UniRAG: Unified Query Understanding Method for Retrieval Augmented Generation_chunk_001]
 根据已有信息，无法回答FaithfulRAG在“处理查询理解方面”的核心创新。所提供的FaithfulRAG片段主要聚焦于生成阶段的知识冲突解决（如自我事实挖掘、自我思考模块），未涉及查询理解或查询增强的相关描述。</t>
-  </si>
-  <si>
-    <t>比较MEMERAG和DragonBall两个基准的异同点，它们各自关注的评估维度是什么？</t>
-  </si>
-  <si>
-    <t>相同点：两者都是多语言RAG评估基准。不同点：MEMERAG专注于多语言端到端元评估，使用母语问题并由专家评估忠实度和相关性；DragonBall是一个多场景多语言RAG全能基准，涵盖金融、法律、医疗领域，包含6,711个问题，用于评估RAG系统在不同场景下的性能。</t>
   </si>
   <si>
     <t>MEMERAG和DragonBall都是用于评估RAG系统的基准，但它们的侧重点和构建方式存在差异。
@@ -478,136 +605,22 @@
     1.  **完整性 (Completeness)**：衡量生成答案对基准答案中关键信息的覆盖程度。
     2.  **幻觉 (Hallucination)**：评估生成答案中是否存在与事实不符的内容。
     3.  **无关性 (Irrelevance)**：评估生成答案中是否包含与问题无关的信息。
-    来自: [2025.acl-long.418_RAGEval, 第2页, 2025.acl-long.418_RAGEval_chunk_001]、[2025.acl-long.418_RAGEval, 第5页, 2025.acl-long.418_RAGEval_chunk_004]
+    来自: [RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第2页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_001]、[RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第5页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_004]
 - **MEMERAG** 是一个多语言的端到端元评估基准，其核心是衡量自动评估器与人类判断的相关性。它关注的评估维度是：
     1.  **忠实性 (Faithfulness)**：判断答案是否基于提供的上下文，而非模型自身的世界知识。
     2.  **相关性 (Relevance)**：判断答案是否与提出的问题相关，而不考虑上下文。
-    来自: [2025.acl-long.1101_MEMERAG, 第3页, 2025.acl-long.1101_MEMERAG_chunk_003]、[2025.acl-long.1101_MEMERAG, 第1页, 2025.acl-long.1101_MEMERAG_chunk_000]
+    来自: [MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation, 第3页, MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation_chunk_003]、[MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation, 第1页, MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation_chunk_000]
 **核心差异总结：**
 DragonBall是一个直接评估RAG系统输出质量的基准，其指标（完整性、幻觉、无关性）直接衡量答案本身的好坏。而MEMERAG是一个**元评估**基准，它通过人类标注的忠实性和相关性标签，来评估那些用于自动评价RAG系统的“评估器”本身是否可靠。此外，DragonBall的数据集是自动生成的，而MEMERAG是基于人工标注构建的。
-来自: [2025.acl-long.418_RAGEval, 第2页, 2025.acl-long.418_RAGEval_chunk_001]、[2025.acl-long.1101_MEMERAG, 第1页, 2025.acl-long.1101_MEMERAG_chunk_001]</t>
-  </si>
-  <si>
-    <t>SYNQA 和 RHIO 分别通过什么方式生成训练数据？这两种数据生成策略在提升模型归因能力上有什么不同？</t>
-  </si>
-  <si>
-    <t>SYNQA：通过 LLM 生成式合成完全受上下文支持的 QA 对（正样本），用于微调小模型的归因能力。
-RHIO：通过选择性掩码检索头，让 LLM 自身生成模拟真实错误的不忠实样本（负样本），并与忠实样本进行联合训练。</t>
-  </si>
-  <si>
-    <t>SYNQA 通过生成式方法合成训练数据：从 Wikipedia 选取上下文句子，让大语言模型（Llama 70B）生成完全由这些句子支持的问答对，并加入语义相似的干扰文章，从而确保每条数据都有清晰的归因路径。RHIO 则通过遮蔽检索头来生成不忠实样本，模拟模型内在的错误类型，然后将这些不忠实样本与忠实样本一起用于训练，使模型学会区分忠实与不忠实的输出。
-在提升归因能力上，两者的策略不同：SYNQA 直接训练一个专门的上下文归因模型，使其能够精确识别支持答案的句子，从而在句子级归因任务上提升精确度和召回率，让小模型甚至超越大模型；RHIO 并不直接做归因，而是通过增强模型对上下文忠实性的感知，在生成过程中抑制不忠实内容，从而提升生成结果的上下文忠实度。
-来自: [2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第2页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_002]、[2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第2页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_001]、[2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第1页, 2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_000]、[2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第7页, 2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_008]</t>
-  </si>
-  <si>
-    <t>比较LongBench v2和AGENTGYM应用场景区别。</t>
-  </si>
-  <si>
-    <t>LongBench v2：专注于长上下文理解的多任务评估，包含503个多项选择题，上下文长度从8k到2M单词，涵盖6个主要任务类别，用于评估LLM在长文档理解和推理方面的能力
-AGENTGYM：专注于代理训练和工具使用的环境集合，包含11个不同的交互环境（如Minecraft、ScienceWorld、BabyAI等），用于训练和评估LLM代理在多样化任务中的能力</t>
-  </si>
-  <si>
-    <t>LongBench v2的应用场景是评估大语言模型在真实长上下文多任务中深度理解与推理的能力，涵盖单文档问答、多文档问答、长上下文学习等六类任务。AGENTGYM的应用场景则是评估和训练基于大语言模型的智能体，使其在网页导航、文字游戏、家务任务等七种真实世界场景中执行多轮决策任务。简言之，前者聚焦于静态文本的深度理解与推理评估，后者聚焦于动态交互环境中的智能体行为评估与训练。
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_000]
-来自: [2025.acl-long.1355_AgentGym, 第1页, 2025.acl-long.1355_AgentGym_chunk_000]
-来自: [2025.acl-long.1355_AgentGym, 第1页, 2025.acl-long.1355_AgentGym_chunk_001]</t>
-  </si>
-  <si>
-    <t>Agentic Reasoning 与 AR-MCTS 分别采用什么核心机制来提升复杂推理能力？</t>
-  </si>
-  <si>
-    <t>Agentic Reasoning：动态调用网页搜索、代码执行作为工具，并引入 Mind‑Map 知识图谱智能体作为结构化记忆，存储推理上下文并追踪逻辑关系。
-AR-MCTS：基于蒙特卡洛树搜索（MCTS），在扩展阶段集成主动检索（Active Retrieval） 机制，自动获取逐步推理的高质量标注，渐进式提升多模态大模型的推理能力。</t>
-  </si>
-  <si>
-    <t>Agentic Reasoning 的核心机制是集成外部基于LLM的代理工具（如网页搜索、代码执行和思维导图代理）来增强推理能力。AR-MCTS 的核心机制则是通过主动检索（Active Retrieval）和蒙特卡洛树搜索（MCTS）来逐步提升多模态推理能力。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第1页, 2025.acl-long.1383_Agentic Reasoning_chunk_001] 和 [2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval, 第1页, 2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval_chunk_000]</t>
-  </si>
-  <si>
-    <t>MAIN‑RAG 与 RAG‑Critic 在提升 RAG 系统可靠性方面分别采用了什么核心方法？</t>
-  </si>
-  <si>
-    <t>MAIN‑RAG 采用多智能体协作过滤机制，通过三个 LLM 智能体（Predictor、Judge、Final‑Predictor）对检索文档进行相关性评分和排序，并利用自适应阈值动态过滤噪声文档，无需训练。
-RAG‑Critic 采用批评引导的智能体工作流，首先构建层次化 RAG 错误系统（3 级错误类型，含 4000+ 细粒度标签），然后训练轻量级错误批评模型进行自动错误诊断，最后通过规划智能体根据错误反馈定制并执行修正方案。</t>
+来自: [RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第2页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_001]、[MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation, 第1页, MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation_chunk_001]</t>
   </si>
   <si>
     <t>MAIN‑RAG 采用的核心方法是**免训练的多智能体协同过滤**：通过多个 LLM 智能体对检索文档进行协同评分与排序，并引入一个**自适应阈值机制**，根据文档得分分布动态调整过滤门槛，从而在无需额外训练的情况下滤除噪声文档、提升生成可靠性。  
 RAG‑Critic 采用的核心方法是**基于批评模型的智能体工作流**：先通过数据驱动的错误挖掘构建分层错误体系，再训练一个轻量级错误批评模型，自动给出细粒度错误反馈，并以此指导智能体工作流进行**错误驱动的修正**，从而增强 RAG 系统的可靠性。
-来自: [2025.acl-long.131_MAIN-RAG, 第1页, 2025.acl-long.131_MAIN-RAG_chunk_001]  
-来自: [2025.acl-long.131_MAIN-RAG, 第2页, 2025.acl-long.131_MAIN-RAG_chunk_002]  
-来自: [2025.acl-long.179_RAG-Critic, 第9页, 2025.acl-long.179_RAG-Critic_chunk_010]  
-来自: [2025.acl-long.179_RAG-Critic, 第8页, 2025.acl-long.179_RAG-Critic_chunk_009]</t>
-  </si>
-  <si>
-    <t>在构建可靠的问答（QA）系统时，这QAEncoder与On Synthesizing Data for Context Attribution in Question Answering两篇论文分别侧重于优化系统工作流的哪个阶段？它们各自试图解决的核心痛点是什么？</t>
-  </si>
-  <si>
-    <t>《QAEncoder》侧重于“检索阶段”
-核心痛点：用户的自然语言查询与知识库中的文档之间存在语义和词汇上的鸿沟，导致检索模块无法精准召回相关文档。
-《On Synthesizing Data for Context Attribution... (SYNQA)》侧重于“生成后阶段”
-核心痛点：大语言模型在生成答案时容易产生幻觉，用户很难验证生成的答案是否真的基于提供的上下文，缺乏可解释性和事实依据。</t>
-  </si>
-  <si>
-    <t>QAEncoder侧重于优化QA系统的**检索阶段**，其核心痛点是**文档与用户查询之间的语义鸿沟（document-query gap）**，即文档表示与查询表示不匹配导致难以精准检索到相关文档。
-来自: [2025.acl-long.217_QAEncoder, 第1页, 2025.acl-long.217_QAEncoder_chunk_000]
-On Synthesizing Data for Context Attribution in Question Answering侧重于优化QA系统的**生成后验证/归因阶段**，其核心痛点是**大语言模型（LLM）的幻觉问题**，即生成的答案可能缺乏事实依据，需要将答案内容归因到上下文中的具体证据，以提升可信度。
-来自: [2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第1页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_000]</t>
-  </si>
-  <si>
-    <t>这10篇论文中哪一篇提出了名为"RAG-Guard"的安全防护框架？</t>
-  </si>
-  <si>
-    <t>不可回答类</t>
-  </si>
-  <si>
-    <t>无法回答。</t>
-  </si>
-  <si>
-    <t>"ProLong"模型在训练过程中使用了哪种具体的优化器来处理长序列训练的梯度问题？</t>
-  </si>
-  <si>
-    <t>ProLong模型在训练过程中使用的优化器是AdamW。
-来自: [2025.acl-long.366_How to Train Long-Context Language Models (Effectively), 第13页, 2025.acl-long.366_How to Train Long-Context Language Models (Effectively)_chunk_013]</t>
-  </si>
-  <si>
-    <t>SETR模型在训练时具体的训练时间是多少小时？</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> L-CiteEval基准中使用的NLI模型deberta-base-long-nli的准确率是多少？该模型在哪些具体数据集上进行了训练？</t>
-  </si>
-  <si>
-    <t>论文中是否提到了SYNQA方法在医疗领域的具体应用案例？</t>
-  </si>
-  <si>
-    <t>论文中是否提供了RHIO方法在实时应用场景中的延迟测试数据？</t>
-  </si>
-  <si>
-    <t>Agentic Reasoning框架中使用的Mind-Map agent的具体神经网络架构是什么？</t>
-  </si>
-  <si>
-    <t>根据已有信息，论文仅指出Mind-Map agent的实现是基于DeepSeek-V3大语言模型来执行知识图谱构建和检索，但并未披露其具体的神经网络架构细节。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第2页, 2025.acl-long.1383_Agentic Reasoning_chunk_002] 和 [2025.acl-long.1383_Agentic Reasoning, 第5页, 2025.acl-long.1383_Agentic Reasoning_chunk_004]</t>
-  </si>
-  <si>
-    <t>在CypherBench基准测试中，每个问题模板具体包含多少个训练样本？</t>
-  </si>
-  <si>
-    <t>【总体平均值】</t>
-  </si>
-  <si>
-    <t>【定义类平均值】</t>
-  </si>
-  <si>
-    <t>【方法细节类平均值】</t>
-  </si>
-  <si>
-    <t>【实验结果类平均值】</t>
-  </si>
-  <si>
-    <t>【跨论文比较类平均值】</t>
-  </si>
-  <si>
-    <t>【不可回答类平均值】</t>
+来自: [MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation, 第1页, MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation_chunk_001]  
+来自: [MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation, 第2页, MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation_chunk_002]  
+来自: [RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation, 第9页, RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation_chunk_010]  
+来自: [RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation, 第8页, RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation_chunk_009]</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1065,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="322" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -1063,7 +1076,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -1096,62 +1109,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="252" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="112" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="182" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -1184,18 +1197,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="294" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1228,18 +1241,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="322" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -1272,18 +1285,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="280" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1316,18 +1329,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="238" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1360,18 +1373,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="406" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="182" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -1406,16 +1419,16 @@
     </row>
     <row r="10" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1448,18 +1461,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="294" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1492,18 +1505,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="308" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="140" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -1538,16 +1551,16 @@
     </row>
     <row r="13" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -1582,16 +1595,16 @@
     </row>
     <row r="14" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -1624,18 +1637,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="294" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -1668,18 +1681,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="378" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
@@ -1712,18 +1725,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="406" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -1758,16 +1771,16 @@
     </row>
     <row r="18" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1802,16 +1815,16 @@
     </row>
     <row r="19" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -1844,18 +1857,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="154" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
@@ -1890,16 +1903,16 @@
     </row>
     <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -1934,16 +1947,16 @@
     </row>
     <row r="22" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -1978,16 +1991,16 @@
     </row>
     <row r="23" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2020,18 +2033,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="336" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2064,18 +2077,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="322" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2108,18 +2121,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="210" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -2154,16 +2167,16 @@
     </row>
     <row r="27" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -2196,18 +2209,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="336" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="154" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -2240,18 +2253,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="280" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="126" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
@@ -2284,18 +2297,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="406" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="196" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2328,18 +2341,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="252" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
@@ -2372,18 +2385,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="210" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -2418,16 +2431,16 @@
     </row>
     <row r="33" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -2460,18 +2473,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="364" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -2506,16 +2519,16 @@
     </row>
     <row r="35" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
@@ -2550,16 +2563,16 @@
     </row>
     <row r="36" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="E36" s="2">
         <v>1</v>
@@ -2594,16 +2607,16 @@
     </row>
     <row r="37" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
@@ -2638,16 +2651,16 @@
     </row>
     <row r="38" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -2682,16 +2695,16 @@
     </row>
     <row r="39" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
@@ -2726,16 +2739,16 @@
     </row>
     <row r="40" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -2770,16 +2783,16 @@
     </row>
     <row r="41" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -2814,16 +2827,16 @@
     </row>
     <row r="42" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -2858,16 +2871,16 @@
     </row>
     <row r="43" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E43" s="2">
         <v>1</v>
@@ -2900,18 +2913,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="112" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
@@ -2932,18 +2945,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="238" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="J45" s="2">
         <v>0</v>
@@ -2964,18 +2977,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="84" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
@@ -2996,18 +3009,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="210" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="98" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
@@ -3028,18 +3041,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="98" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -3060,18 +3073,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="98" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -3092,18 +3105,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="322" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -3124,18 +3137,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="126" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -3156,9 +3169,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="E53" s="2">
         <f>AVERAGEIFS(E2:E51,K2:K51,FALSE)</f>
@@ -3197,9 +3210,9 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3241,12 +3254,12 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E55" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"方法细节类",K2:K51,FALSE)</f>
@@ -3285,12 +3298,12 @@
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="E56" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"实验结果类",K2:K51,FALSE)</f>
@@ -3329,12 +3342,12 @@
         <v>0.18181818181818182</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="E57" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
@@ -3373,12 +3386,12 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="E58" s="2" t="e">
         <f>AVERAGEIFS(E2:E51,B2:B51,"不可回答类",K2:K51,FALSE)</f>

--- a/code/experiment/1024chunk_BGE-M3-10topk_Y.xlsx
+++ b/code/experiment/1024chunk_BGE-M3-10topk_Y.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3BDB70-5ED9-49F7-8193-D65789DD43BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27A0DF0-BE80-4AC0-866D-58099193E0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -210,9 +210,6 @@
     <t>根据已有信息，无法回答此问题。</t>
   </si>
   <si>
-    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
-  </si>
-  <si>
     <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
   </si>
   <si>
@@ -621,6 +618,10 @@
 来自: [MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation, 第2页, MAIN-RAG: Multi-Agent Filtering Retrieval-Augmented Generation_chunk_002]  
 来自: [RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation, 第9页, RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation_chunk_010]  
 来自: [RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation, 第8页, RAG-Critic: Leveraging Automated Critic-Guided Agentic Workflow for Retrieval Augmented Generation_chunk_009]</t>
+  </si>
+  <si>
+    <t>CypherBench 提出了什么核心方法来应对 RDF 查询的挑战？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1065,7 +1066,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="322" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="294" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -1076,7 +1077,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -1109,7 +1110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="112" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="266" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -1120,7 +1121,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E3" s="2">
         <v>0</v>
@@ -1153,7 +1154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="182" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="308" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1164,7 +1165,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -1197,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="294" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -1208,7 +1209,7 @@
         <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1241,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="322" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="280" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -1252,7 +1253,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -1296,7 +1297,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1329,7 +1330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="238" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="350" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1340,7 +1341,7 @@
         <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1373,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="182" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -1384,7 +1385,7 @@
         <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -1428,7 +1429,7 @@
         <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1472,7 +1473,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1505,7 +1506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="140" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="280" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -1516,7 +1517,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -1549,7 +1550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="392" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -1560,7 +1561,7 @@
         <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -1604,7 +1605,7 @@
         <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -1637,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="294" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
@@ -1648,7 +1649,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -1681,7 +1682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="378" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="364" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
@@ -1692,7 +1693,7 @@
         <v>46</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
@@ -1725,7 +1726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="406" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
@@ -1736,7 +1737,7 @@
         <v>48</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -1780,7 +1781,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1824,7 +1825,7 @@
         <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -1903,16 +1904,16 @@
     </row>
     <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -1947,16 +1948,16 @@
     </row>
     <row r="22" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -1991,16 +1992,16 @@
     </row>
     <row r="23" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2033,18 +2034,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="336" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2077,18 +2078,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="322" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2121,18 +2122,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="210" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="378" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -2167,16 +2168,16 @@
     </row>
     <row r="27" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -2209,18 +2210,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="154" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="224" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -2253,18 +2254,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="126" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="266" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
@@ -2297,18 +2298,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="196" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="308" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2341,18 +2342,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="252" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="364" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
@@ -2385,18 +2386,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="210" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="322" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -2431,16 +2432,16 @@
     </row>
     <row r="33" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -2473,18 +2474,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="364" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -2519,16 +2520,16 @@
     </row>
     <row r="35" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
@@ -2563,16 +2564,16 @@
     </row>
     <row r="36" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E36" s="2">
         <v>1</v>
@@ -2607,16 +2608,16 @@
     </row>
     <row r="37" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
@@ -2651,16 +2652,16 @@
     </row>
     <row r="38" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -2695,16 +2696,16 @@
     </row>
     <row r="39" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
@@ -2739,16 +2740,16 @@
     </row>
     <row r="40" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -2783,16 +2784,16 @@
     </row>
     <row r="41" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -2827,16 +2828,16 @@
     </row>
     <row r="42" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -2871,16 +2872,16 @@
     </row>
     <row r="43" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E43" s="2">
         <v>1</v>
@@ -2915,13 +2916,13 @@
     </row>
     <row r="44" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>55</v>
@@ -2945,18 +2946,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="238" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="224" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="D45" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J45" s="2">
         <v>0</v>
@@ -2979,13 +2980,13 @@
     </row>
     <row r="46" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>55</v>
@@ -3011,13 +3012,13 @@
     </row>
     <row r="47" spans="1:15" ht="98" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>55</v>
@@ -3043,13 +3044,13 @@
     </row>
     <row r="48" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>55</v>
@@ -3075,13 +3076,13 @@
     </row>
     <row r="49" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>55</v>
@@ -3105,18 +3106,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="322" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="D50" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -3139,13 +3140,13 @@
     </row>
     <row r="51" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>55</v>
@@ -3171,7 +3172,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E53" s="2">
         <f>AVERAGEIFS(E2:E51,K2:K51,FALSE)</f>
@@ -3212,7 +3213,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3256,7 +3257,7 @@
     </row>
     <row r="55" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>41</v>
@@ -3300,10 +3301,10 @@
     </row>
     <row r="56" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E56" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"实验结果类",K2:K51,FALSE)</f>
@@ -3344,10 +3345,10 @@
     </row>
     <row r="57" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E57" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
@@ -3388,10 +3389,10 @@
     </row>
     <row r="58" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E58" s="2" t="e">
         <f>AVERAGEIFS(E2:E51,B2:B51,"不可回答类",K2:K51,FALSE)</f>
